--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -431,12 +431,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bsmyley0@berkeley.edu</t>
+          <t>ibrahimfakhreyams@gmail.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?h&lt;Cj={98@|&gt;</t>
+          <t>0\)oQ.xMl.+C</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5@kl88Y`U4!o</t>
+          <t>"Sc&lt;JgCa'OYE</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L/xf%nI|;*_h</t>
+          <t>)3mS'6ak.4:c</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>otxJa&lt;~o/%@~</t>
+          <t>}Il2syB9j`87</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>}ud`Xr[z@fnJ</t>
+          <t>{aQd_,YPfvy'</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d-Bs,+n~zf9+</t>
+          <t>S3*{5Br[}vD&amp;</t>
         </is>
       </c>
     </row>

--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,72 +431,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ibrahimfakhreyams@gmail.com</t>
+          <t>rmineghelli0@last.fm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0\)oQ.xMl.+C</t>
+          <t>zg26lKJiDifT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brooze1@aboutads.info</t>
+          <t>mbradberry1@netlog.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"Sc&lt;JgCa'OYE</t>
+          <t>J2vK4Z0UPA24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ggammon2@biglobe.ne.jp</t>
+          <t>bcrowdy2@theglobeandmail.com</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>)3mS'6ak.4:c</t>
+          <t>dgtbreUdXCZd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>henoch3@mashable.com</t>
+          <t>jmazzei3@i2i.jp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>}Il2syB9j`87</t>
+          <t>koy0xcoGW4Gf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mde4@simplemachines.org</t>
+          <t>goleagham4@archive.org</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{aQd_,YPfvy'</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>jforrest5@cam.ac.uk</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>S3*{5Br[}vD&amp;</t>
+          <t>aHtHomi9GOm5</t>
         </is>
       </c>
     </row>

--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zg26lKJiDifT</t>
+          <t>CzCTsCA1gXa0</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J2vK4Z0UPA24</t>
+          <t>7yef7TEAqZdF</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dgtbreUdXCZd</t>
+          <t>dlEua48y7RI0</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>koy0xcoGW4Gf</t>
+          <t>0dkb40TV49Mj</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>aHtHomi9GOm5</t>
+          <t>0SHc45Qjj0iF</t>
         </is>
       </c>
     </row>

--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CzCTsCA1gXa0</t>
+          <t>GMBYKFFwwdmj</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7yef7TEAqZdF</t>
+          <t>zu5NUH5OLbBO</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dlEua48y7RI0</t>
+          <t>ak5FXZdYyG7j</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0dkb40TV49Mj</t>
+          <t>WWNEHbZeJ1QS</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0SHc45Qjj0iF</t>
+          <t>KIiBWtyowGQG</t>
         </is>
       </c>
     </row>

--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GMBYKFFwwdmj</t>
+          <t>Oo7Qc7CAEaZc</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>zu5NUH5OLbBO</t>
+          <t>vNf616Q3An1Y</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ak5FXZdYyG7j</t>
+          <t>d3YRFhvh1TeH</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WWNEHbZeJ1QS</t>
+          <t>QEpbE9gOBCcm</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KIiBWtyowGQG</t>
+          <t>rM1DKfXF9Tnu</t>
         </is>
       </c>
     </row>

--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oo7Qc7CAEaZc</t>
+          <t>ScQKE1NWj1e6</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vNf616Q3An1Y</t>
+          <t>u5medhT0Xrcy</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d3YRFhvh1TeH</t>
+          <t>mTQlmYt5rLBR</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QEpbE9gOBCcm</t>
+          <t>XkG2P41ryQJN</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rM1DKfXF9Tnu</t>
+          <t>xtrx9pxoJKOn</t>
         </is>
       </c>
     </row>

--- a/media/created_members.xlsx
+++ b/media/created_members.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ScQKE1NWj1e6</t>
+          <t>LlmffrYeTK6s</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>u5medhT0Xrcy</t>
+          <t>TeFQpZ9EvOua</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mTQlmYt5rLBR</t>
+          <t>1L8u5s4lFozr</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XkG2P41ryQJN</t>
+          <t>fWk4Sgco9yvZ</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xtrx9pxoJKOn</t>
+          <t>kpJfZxKMeRQl</t>
         </is>
       </c>
     </row>
